--- a/docs/software-engineering/Rentino-Phase1-MSP.xlsx
+++ b/docs/software-engineering/Rentino-Phase1-MSP.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>امیررضا</t>
+          <t>امیررضا زارع</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>امیررضا</t>
+          <t>امیررضا زارع</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>امیررضا</t>
+          <t>امیررضا زارع</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>امیررضا</t>
+          <t>امیررضا زارع</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>امیررضا</t>
+          <t>امیررضا زارع</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
